--- a/data/trans_orig/P24B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>29085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>51230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81642</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226991</t>
+          <t>225018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257600</t>
+          <t>257030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103536</t>
+          <t>103155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>337524</t>
+          <t>337412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374887</t>
+          <t>374734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26787</t>
+          <t>26596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45376</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72949</t>
+          <t>72755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75045</t>
+          <t>73310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>56928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83631</t>
+          <t>84263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120207</t>
+          <t>121857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>271944</t>
+          <t>273549</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>310198</t>
+          <t>311880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156335</t>
+          <t>156870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>409196</t>
+          <t>409037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458034</t>
+          <t>458143</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>70813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31115</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55323</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79485</t>
+          <t>79570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>115676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40612</t>
+          <t>40769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67306</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66301</t>
+          <t>66642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99852</t>
+          <t>98956</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152716</t>
+          <t>153057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183581</t>
+          <t>184154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84288</t>
+          <t>83190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109322</t>
+          <t>108787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242896</t>
+          <t>243182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284299</t>
+          <t>281776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>59251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>95497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50212</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79360</t>
+          <t>79252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77631</t>
+          <t>78890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109238</t>
+          <t>107841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148234</t>
+          <t>150745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>252772</t>
+          <t>255402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289616</t>
+          <t>292639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154659</t>
+          <t>156194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189209</t>
+          <t>191153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418575</t>
+          <t>418692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>469108</t>
+          <t>472619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55805</t>
+          <t>54149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86960</t>
+          <t>84050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83210</t>
+          <t>83490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117422</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159518</t>
+          <t>159291</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>189440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243889</t>
+          <t>242929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>138394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185240</t>
+          <t>184899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413113</t>
+          <t>412919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>940124</t>
+          <t>939685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1007518</t>
+          <t>1008922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>500371</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>557430</t>
+          <t>555900</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1456691</t>
+          <t>1455238</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1544929</t>
+          <t>1549496</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217492</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>155027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200007</t>
+          <t>200549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335468</t>
+          <t>335610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>405865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58515</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>89369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25502</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>47457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89945</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126088</t>
+          <t>127827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135636</t>
+          <t>137082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168867</t>
+          <t>170474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73895</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100567</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220211</t>
+          <t>219793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263284</t>
+          <t>262402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57752</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50743</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>63633</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98125</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>117230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156733</t>
+          <t>157027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57957</t>
+          <t>60271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90998</t>
+          <t>91362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186880</t>
+          <t>184390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237051</t>
+          <t>235106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174246</t>
+          <t>173025</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>213956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137361</t>
+          <t>138569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174390</t>
+          <t>172222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>325649</t>
+          <t>325683</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>379072</t>
+          <t>380057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46076</t>
+          <t>46376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112738</t>
+          <t>111645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156077</t>
+          <t>155260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82310</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118306</t>
+          <t>118319</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53754</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>82430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143998</t>
+          <t>143137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188552</t>
+          <t>189911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144023</t>
+          <t>144932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181089</t>
+          <t>183417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92513</t>
+          <t>91790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123634</t>
+          <t>123913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245561</t>
+          <t>244671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295328</t>
+          <t>294908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67493</t>
+          <t>67195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>68730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88735</t>
+          <t>89224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128922</t>
+          <t>127502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81407</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116366</t>
+          <t>116824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65238</t>
+          <t>66579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96476</t>
+          <t>97542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159510</t>
+          <t>157128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207597</t>
+          <t>203923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199713</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238769</t>
+          <t>237359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141911</t>
+          <t>141757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175708</t>
+          <t>176563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351953</t>
+          <t>351197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404139</t>
+          <t>403918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35593</t>
+          <t>35110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41225</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82973</t>
+          <t>83516</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120315</t>
+          <t>120595</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>367083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>443939</t>
+          <t>439573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229081</t>
+          <t>229976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286122</t>
+          <t>286682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>621589</t>
+          <t>618292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>709990</t>
+          <t>712119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>692007</t>
+          <t>694759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>769000</t>
+          <t>774568</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>480057</t>
+          <t>477272</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>546715</t>
+          <t>543528</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1191731</t>
+          <t>1191545</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1289279</t>
+          <t>1288048</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191076</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245250</t>
+          <t>247602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181764</t>
+          <t>182084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>234812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>383356</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>464289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37343</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63212</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39875</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95025</t>
+          <t>93479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161778</t>
+          <t>161792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190355</t>
+          <t>190899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107836</t>
+          <t>107167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130823</t>
+          <t>131300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278151</t>
+          <t>275002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314940</t>
+          <t>314313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>59010</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85948</t>
+          <t>83394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>44751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70919</t>
+          <t>71958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105669</t>
+          <t>104011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147372</t>
+          <t>145286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210743</t>
+          <t>207861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245544</t>
+          <t>243742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>156114</t>
+          <t>158099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189296</t>
+          <t>189664</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>376793</t>
+          <t>375453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>424041</t>
+          <t>425474</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>26151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51138</t>
+          <t>51572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>61078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67282</t>
+          <t>68806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68516</t>
+          <t>69027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90876</t>
+          <t>91381</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129542</t>
+          <t>127483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200248</t>
+          <t>199985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234017</t>
+          <t>233049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131164</t>
+          <t>131029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160375</t>
+          <t>159942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337714</t>
+          <t>340726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385107</t>
+          <t>385240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>33608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44300</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76497</t>
+          <t>75933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>103661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44162</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>73148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126578</t>
+          <t>125362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170316</t>
+          <t>168119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>135547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167059</t>
+          <t>166486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>140758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171856</t>
+          <t>170870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283138</t>
+          <t>282374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328873</t>
+          <t>330874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>53579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68157</t>
+          <t>67708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>102117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230964</t>
+          <t>229114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289075</t>
+          <t>286366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175320</t>
+          <t>175165</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225064</t>
+          <t>223493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>417022</t>
+          <t>418432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>493559</t>
+          <t>495660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>740944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>807654</t>
+          <t>807270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>568218</t>
+          <t>566155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>623617</t>
+          <t>624421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1321097</t>
+          <t>1324660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1408880</t>
+          <t>1411452</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116593</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163319</t>
+          <t>162662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142982</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233676</t>
+          <t>232895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295304</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54111</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51230</t>
+          <t>50893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81991</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225018</t>
+          <t>226044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257030</t>
+          <t>255822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103155</t>
+          <t>103934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125433</t>
+          <t>126976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>337412</t>
+          <t>337731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374734</t>
+          <t>375544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44593</t>
+          <t>44294</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72755</t>
+          <t>72794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>44239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73310</t>
+          <t>74056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56928</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84263</t>
+          <t>82832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121857</t>
+          <t>121209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273549</t>
+          <t>275032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311880</t>
+          <t>311928</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126018</t>
+          <t>127113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156870</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>409037</t>
+          <t>410400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458143</t>
+          <t>457966</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70813</t>
+          <t>70715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>56369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79570</t>
+          <t>80783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115676</t>
+          <t>117733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66642</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98956</t>
+          <t>98176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153057</t>
+          <t>152540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184154</t>
+          <t>182622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83190</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108787</t>
+          <t>106875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243182</t>
+          <t>244305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281776</t>
+          <t>284446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44318</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36188</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>59074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62244</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95497</t>
+          <t>94734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79252</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78890</t>
+          <t>78805</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>108099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150745</t>
+          <t>151460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>255402</t>
+          <t>253813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292639</t>
+          <t>292518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156194</t>
+          <t>155361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191153</t>
+          <t>191859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418692</t>
+          <t>419518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472619</t>
+          <t>472612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84050</t>
+          <t>85846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53630</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>116339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>159291</t>
+          <t>159057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189440</t>
+          <t>188031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242929</t>
+          <t>242758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138394</t>
+          <t>138517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>184218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340076</t>
+          <t>344624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>416003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>940290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1008922</t>
+          <t>1011181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>499663</t>
+          <t>498398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>555900</t>
+          <t>553817</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1455238</t>
+          <t>1457953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1549496</t>
+          <t>1542820</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164819</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155027</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200549</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335610</t>
+          <t>334350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405865</t>
+          <t>404758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59153</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>87404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91092</t>
+          <t>91869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127827</t>
+          <t>126066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137082</t>
+          <t>138924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170474</t>
+          <t>170418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100479</t>
+          <t>101565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219793</t>
+          <t>219487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262402</t>
+          <t>262166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>32519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50344</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63633</t>
+          <t>64777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117230</t>
+          <t>116366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>156637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>59908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91362</t>
+          <t>90511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184390</t>
+          <t>186603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235106</t>
+          <t>236270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173025</t>
+          <t>172024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>213956</t>
+          <t>216155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138569</t>
+          <t>139418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172222</t>
+          <t>174096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>325683</t>
+          <t>327002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>380057</t>
+          <t>380104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91202</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>45494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74206</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111645</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155260</t>
+          <t>155121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81616</t>
+          <t>79937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>116814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>53961</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82430</t>
+          <t>83685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143137</t>
+          <t>146648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189911</t>
+          <t>192040</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144932</t>
+          <t>145702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183417</t>
+          <t>182335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91790</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123913</t>
+          <t>123008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244671</t>
+          <t>247528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294908</t>
+          <t>295704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39818</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67195</t>
+          <t>69423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>41384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68730</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127502</t>
+          <t>127248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82846</t>
+          <t>82837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>66726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97542</t>
+          <t>97161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157128</t>
+          <t>157810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203923</t>
+          <t>204279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>199028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237359</t>
+          <t>235845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141757</t>
+          <t>140870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176563</t>
+          <t>176787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351197</t>
+          <t>351327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>403918</t>
+          <t>403582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>61705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40952</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>67601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83516</t>
+          <t>83837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>120357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>367083</t>
+          <t>369359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>439573</t>
+          <t>445012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229976</t>
+          <t>229875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286682</t>
+          <t>286355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618292</t>
+          <t>624268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>712119</t>
+          <t>709832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>694759</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>774568</t>
+          <t>769989</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>477272</t>
+          <t>479688</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>543528</t>
+          <t>545286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1191545</t>
+          <t>1191531</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1288048</t>
+          <t>1289185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>247602</t>
+          <t>245552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182084</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>234812</t>
+          <t>232260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>387055</t>
+          <t>387386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464289</t>
+          <t>461151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>36539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61120</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>39557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61884</t>
+          <t>61502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93479</t>
+          <t>93171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161792</t>
+          <t>160593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190899</t>
+          <t>189854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107167</t>
+          <t>107588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275002</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314313</t>
+          <t>315526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59010</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52468</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83394</t>
+          <t>84046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44751</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71958</t>
+          <t>72131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104011</t>
+          <t>103630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145286</t>
+          <t>145963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>207861</t>
+          <t>210257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>243742</t>
+          <t>245249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158099</t>
+          <t>155087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>189664</t>
+          <t>188850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>375453</t>
+          <t>378192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>425474</t>
+          <t>424697</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26616</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>51867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61078</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94740</t>
+          <t>94059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68806</t>
+          <t>70368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>42083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>67445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91381</t>
+          <t>89987</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127483</t>
+          <t>129716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199985</t>
+          <t>200019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233049</t>
+          <t>234306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131029</t>
+          <t>131993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159942</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340726</t>
+          <t>339924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385240</t>
+          <t>384548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>33375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75933</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73650</t>
+          <t>71834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103661</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73148</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125362</t>
+          <t>126254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168119</t>
+          <t>167810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135547</t>
+          <t>133113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>169056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140758</t>
+          <t>139641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170870</t>
+          <t>171349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282374</t>
+          <t>282999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330874</t>
+          <t>327235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30925</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>55687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67708</t>
+          <t>68016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>102117</t>
+          <t>102588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229114</t>
+          <t>229356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286366</t>
+          <t>287286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>174032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223493</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>420110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495660</t>
+          <t>495334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>740944</t>
+          <t>741170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>807270</t>
+          <t>806208</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>566155</t>
+          <t>568299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>624421</t>
+          <t>627045</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1324660</t>
+          <t>1325833</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1411452</t>
+          <t>1410439</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118020</t>
+          <t>118603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>145935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232895</t>
+          <t>231646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295610</t>
+          <t>292687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
